--- a/Professional/3-PhD/1-Fellowships/Fellowship-Finder.xlsx
+++ b/Professional/3-PhD/1-Fellowships/Fellowship-Finder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scott\Documents\Folder\Professional\3-PhD\1-Fellowships\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F557D4D-24DC-4697-B025-BC62AFEFF5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258CC0DE-A8D4-451A-A601-46B2C1774D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{62D280D6-400F-4111-B152-A7E32F9952F6}"/>
+    <workbookView xWindow="5300" yWindow="3060" windowWidth="17280" windowHeight="10690" xr2:uid="{62D280D6-400F-4111-B152-A7E32F9952F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
